--- a/Dataset_combinato_GPS_finale.xlsx
+++ b/Dataset_combinato_GPS_finale.xlsx
@@ -5626,12 +5626,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -9168,12 +9168,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -9340,12 +9340,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -9598,12 +9598,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>Udinese</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Milan</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">

--- a/Dataset_combinato_GPS_finale.xlsx
+++ b/Dataset_combinato_GPS_finale.xlsx
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Test_Match</t>
+          <t>Test Match</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
